--- a/data/trans_dic/IP04D$individual-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -612,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -675,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,14; 25,96</t>
+          <t>10,39; 26,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,94; 58,16</t>
+          <t>37,31; 57,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,02; 37,88</t>
+          <t>19,42; 38,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,89; 40,78</t>
+          <t>21,8; 40,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,43; 42,65</t>
+          <t>23,0; 42,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,47; 52,22</t>
+          <t>32,1; 52,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,0; 32,13</t>
+          <t>18,67; 31,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,82; 47,55</t>
+          <t>32,36; 46,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,05; 42,16</t>
+          <t>28,29; 42,75</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -785,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,16; 26,55</t>
+          <t>14,4; 26,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,5; 47,12</t>
+          <t>31,65; 46,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 4,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,8; 30,95</t>
+          <t>17,77; 30,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,8; 45,88</t>
+          <t>30,28; 45,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,69</t>
+          <t>0,32; 3,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,29; 27,09</t>
+          <t>17,75; 26,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,35; 43,65</t>
+          <t>32,79; 43,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,31</t>
+          <t>0,5; 3,12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,68; 31,72</t>
+          <t>14,48; 31,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,93; 25,61</t>
+          <t>10,88; 27,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,09; 29,76</t>
+          <t>13,07; 28,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,51; 29,29</t>
+          <t>12,69; 28,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,98; 26,23</t>
+          <t>11,08; 25,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 25,72</t>
+          <t>10,37; 25,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,6; 27,13</t>
+          <t>15,57; 27,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,21; 23,51</t>
+          <t>12,8; 23,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,15; 24,1</t>
+          <t>13,26; 24,02</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,58; 41,02</t>
+          <t>24,32; 40,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,6; 40,37</t>
+          <t>22,88; 40,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,01; 58,53</t>
+          <t>37,73; 58,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,25; 45,65</t>
+          <t>26,46; 45,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,37; 34,79</t>
+          <t>18,78; 35,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,1; 77,53</t>
+          <t>42,93; 75,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,15; 41,04</t>
+          <t>27,78; 41,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,74; 35,13</t>
+          <t>22,78; 34,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,31; 63,89</t>
+          <t>44,7; 65,28</t>
         </is>
       </c>
     </row>
@@ -1115,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,99; 34,64</t>
+          <t>12,3; 34,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,35; 19,82</t>
+          <t>3,42; 20,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 8,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,79; 35,89</t>
+          <t>14,69; 36,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 21,53</t>
+          <t>4,95; 19,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,13; 31,41</t>
+          <t>15,79; 31,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,44; 15,75</t>
+          <t>5,15; 16,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1225,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,31; 37,32</t>
+          <t>17,5; 37,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,07; 49,3</t>
+          <t>27,12; 47,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 16,1</t>
+          <t>3,16; 17,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,02; 28,93</t>
+          <t>11,78; 28,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,62; 42,63</t>
+          <t>21,05; 42,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,73; 33,83</t>
+          <t>12,62; 33,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,41; 30,58</t>
+          <t>16,92; 30,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,53; 41,14</t>
+          <t>26,68; 41,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,24; 22,75</t>
+          <t>10,29; 23,22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1335,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,54; 27,09</t>
+          <t>15,55; 27,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,73; 34,27</t>
+          <t>21,27; 33,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,59; 32,4</t>
+          <t>18,72; 32,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,05; 28,86</t>
+          <t>16,76; 28,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,5; 34,51</t>
+          <t>21,49; 34,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,2; 38,27</t>
+          <t>23,17; 38,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,68; 25,67</t>
+          <t>18,01; 26,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,36; 32,07</t>
+          <t>23,2; 32,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,67; 33,51</t>
+          <t>22,49; 33,62</t>
         </is>
       </c>
     </row>
@@ -1445,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>39,6; 52,44</t>
+          <t>39,9; 52,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,83; 41,7</t>
+          <t>29,53; 41,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,7</t>
+          <t>1,7; 7,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47,72; 60,42</t>
+          <t>47,28; 59,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,19; 37,74</t>
+          <t>26,35; 38,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,37</t>
+          <t>1,79; 7,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,45; 54,12</t>
+          <t>45,37; 54,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,58; 37,59</t>
+          <t>29,9; 37,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,13</t>
+          <t>2,36; 6,12</t>
         </is>
       </c>
     </row>
@@ -1555,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25,48; 30,94</t>
+          <t>25,65; 31,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28,96; 34,57</t>
+          <t>28,87; 34,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,62; 18,88</t>
+          <t>13,14; 18,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29,13; 34,51</t>
+          <t>28,85; 34,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26,08; 31,18</t>
+          <t>25,72; 31,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,69; 24,76</t>
+          <t>17,63; 25,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,0; 32,0</t>
+          <t>27,92; 31,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28,25; 32,25</t>
+          <t>28,46; 32,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,39; 21,11</t>
+          <t>16,44; 21,29</t>
         </is>
       </c>
     </row>
@@ -1624,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9708</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>27425</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20308</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20368</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21027</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>33079</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30076</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>48452</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>53387</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5868; 14893</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21403; 33221</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14230; 28497</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14129; 26378</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14826; 27316</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>25480; 41558</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>22637; 38274</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>39421; 57095</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>43184; 65250</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>20837</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40841</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1662</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>41866</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>47207</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>82707</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3559</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>14983; 28069</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>32902; 48596</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5391</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19522; 33965</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>33393; 50365</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>403; 4742</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>37969; 57620</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>70248; 94022</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1277; 7963</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>15209</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11965</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11763</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14217</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12016</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11197</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>29426</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>23981</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>22960</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>9875; 21248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7272; 18167</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7616; 16705</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9043; 20365</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7745; 17618</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6966; 17162</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>21711; 38483</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>17499; 32808</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>16626; 30132</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>24716</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23476</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32867</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29447</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>21243</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45654</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>54163</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>44718</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>78521</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>18912; 31802</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17414; 30590</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>26087; 40780</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>21761; 37029</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>15249; 29112</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>33545; 58658</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>44453; 65860</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>35834; 54253</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>65828; 96146</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>10044</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3773</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11363</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4880</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>21407</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>8653</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5401; 14956</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1396; 8268</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2841</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6867; 17216</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2295; 9213</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14314; 28929</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>4495; 14520</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3302</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>14726</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19941</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4056</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>11866</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>17869</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>12099</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>26592</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>37810</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>16155</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>9677; 20711</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>14719; 25685</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1459; 8106</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>7098; 17057</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>12151; 24672</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>7091; 18658</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>19549; 35087</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>29883; 46603</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>10537; 23771</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>29385</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>37288</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>30919</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>32329</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>38812</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>46376</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>61714</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>76100</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>77295</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>21575; 37685</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>29057; 46432</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>23311; 40672</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>24427; 41306</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>30066; 48698</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>35937; 60185</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>51228; 74588</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>64150; 89282</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>62883; 93988</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>75284</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>58037</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>5303</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>92061</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>54326</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>6013</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>167345</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>112362</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>11316</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>65403; 85973</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>48479; 67573</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2236; 9651</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>80994; 102441</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>44837; 64968</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2801; 11186</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>152101; 181882</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>99972; 126924</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>6785; 17616</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>199908</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>222745</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>107431</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>238021</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>212039</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>156315</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>437929</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>434784</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>263747</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>181701; 221031</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>202173; 242461</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>87393; 123999</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>217052; 258778</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>190319; 232392</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>134069; 191362</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>407801; 466932</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>409889; 465742</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>234280; 303437</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$individual-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,39; 26,38</t>
+          <t>10,8; 26,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37,31; 57,91</t>
+          <t>35,13; 57,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,42; 38,89</t>
+          <t>18,48; 37,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,8; 40,7</t>
+          <t>21,71; 40,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,0; 42,37</t>
+          <t>23,56; 42,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,1; 52,36</t>
+          <t>31,26; 52,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,67; 31,56</t>
+          <t>18,82; 31,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,36; 46,86</t>
+          <t>32,97; 46,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,29; 42,75</t>
+          <t>28,42; 43,58</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,4; 26,97</t>
+          <t>14,27; 26,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,65; 46,75</t>
+          <t>31,42; 47,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,22</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,77; 30,91</t>
+          <t>17,93; 31,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,28; 45,67</t>
+          <t>30,85; 45,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,72</t>
+          <t>0,51; 3,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,75; 26,93</t>
+          <t>17,56; 26,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,79; 43,89</t>
+          <t>33,3; 44,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,12</t>
+          <t>0,55; 2,89</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,48; 31,17</t>
+          <t>15,16; 32,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,88; 27,18</t>
+          <t>10,28; 26,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,07; 28,67</t>
+          <t>13,55; 29,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,69; 28,58</t>
+          <t>12,77; 29,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 25,2</t>
+          <t>10,23; 26,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,37; 25,55</t>
+          <t>10,31; 24,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,57; 27,6</t>
+          <t>15,43; 27,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,8; 23,99</t>
+          <t>12,55; 23,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,26; 24,02</t>
+          <t>13,57; 24,3</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,32; 40,9</t>
+          <t>23,51; 40,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,88; 40,18</t>
+          <t>22,39; 40,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,73; 58,98</t>
+          <t>37,49; 57,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,46; 45,03</t>
+          <t>26,68; 44,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,78; 35,86</t>
+          <t>19,08; 35,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,93; 75,07</t>
+          <t>43,99; 75,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,78; 41,16</t>
+          <t>28,19; 40,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,78; 34,49</t>
+          <t>22,54; 34,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44,7; 65,28</t>
+          <t>44,03; 65,96</t>
         </is>
       </c>
     </row>
@@ -1118,27 +1118,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,3; 34,07</t>
+          <t>13,98; 36,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 20,24</t>
+          <t>3,27; 20,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,23</t>
+          <t>0,0; 8,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,69; 36,82</t>
+          <t>15,2; 35,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 19,88</t>
+          <t>4,93; 20,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,79; 31,91</t>
+          <t>16,91; 31,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 16,65</t>
+          <t>5,38; 16,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,5; 37,46</t>
+          <t>17,9; 37,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,12; 47,33</t>
+          <t>26,21; 48,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,16; 17,56</t>
+          <t>3,09; 17,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,78; 28,31</t>
+          <t>12,3; 29,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,05; 42,73</t>
+          <t>21,03; 43,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,62; 33,21</t>
+          <t>13,43; 34,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,92; 30,37</t>
+          <t>16,27; 29,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,68; 41,61</t>
+          <t>26,64; 41,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,29; 23,22</t>
+          <t>10,36; 23,25</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,55; 27,17</t>
+          <t>15,38; 27,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,27; 33,99</t>
+          <t>21,6; 33,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,72; 32,67</t>
+          <t>18,63; 31,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,76; 28,34</t>
+          <t>16,86; 28,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,49; 34,81</t>
+          <t>21,65; 33,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,17; 38,81</t>
+          <t>23,54; 39,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,01; 26,22</t>
+          <t>17,4; 25,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,2; 32,29</t>
+          <t>22,45; 31,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,49; 33,62</t>
+          <t>22,99; 33,49</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>39,9; 52,45</t>
+          <t>39,8; 52,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,53; 41,16</t>
+          <t>29,8; 41,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,33</t>
+          <t>1,95; 7,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47,28; 59,8</t>
+          <t>47,58; 59,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,35; 38,18</t>
+          <t>26,31; 37,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,79; 7,17</t>
+          <t>1,84; 7,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,37; 54,26</t>
+          <t>45,47; 54,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,9; 37,96</t>
+          <t>29,6; 38,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,12</t>
+          <t>2,36; 6,1</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25,65; 31,21</t>
+          <t>25,4; 31,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28,87; 34,63</t>
+          <t>29,0; 34,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,14; 18,64</t>
+          <t>13,43; 19,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28,85; 34,4</t>
+          <t>28,9; 34,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,72; 31,4</t>
+          <t>26,14; 31,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,63; 25,17</t>
+          <t>17,7; 24,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,92; 31,97</t>
+          <t>28,01; 32,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28,46; 32,34</t>
+          <t>28,13; 32,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,44; 21,29</t>
+          <t>16,32; 21,11</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5868; 14893</t>
+          <t>6096; 15104</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21403; 33221</t>
+          <t>20157; 32758</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14230; 28497</t>
+          <t>13543; 27183</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14129; 26378</t>
+          <t>14071; 26312</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14826; 27316</t>
+          <t>15184; 27439</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25480; 41558</t>
+          <t>24813; 41423</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22637; 38274</t>
+          <t>22822; 38072</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39421; 57095</t>
+          <t>40166; 57169</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43184; 65250</t>
+          <t>43379; 66529</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14983; 28069</t>
+          <t>14853; 27850</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32902; 48596</t>
+          <t>32662; 49270</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5391</t>
+          <t>0; 5422</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19522; 33965</t>
+          <t>19706; 34709</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33393; 50365</t>
+          <t>34024; 50695</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>403; 4742</t>
+          <t>645; 4824</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37969; 57620</t>
+          <t>37562; 57195</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70248; 94022</t>
+          <t>71333; 94705</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1277; 7963</t>
+          <t>1405; 7368</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9875; 21248</t>
+          <t>10334; 22103</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7272; 18167</t>
+          <t>6867; 17702</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7616; 16705</t>
+          <t>7893; 16965</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9043; 20365</t>
+          <t>9096; 20807</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7745; 17618</t>
+          <t>7154; 18197</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6966; 17162</t>
+          <t>6927; 16587</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21711; 38483</t>
+          <t>21515; 38087</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17499; 32808</t>
+          <t>17157; 31657</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16626; 30132</t>
+          <t>17019; 30483</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18912; 31802</t>
+          <t>18279; 31736</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17414; 30590</t>
+          <t>17048; 30560</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26087; 40780</t>
+          <t>25925; 39756</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21761; 37029</t>
+          <t>21941; 36714</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15249; 29112</t>
+          <t>15487; 28608</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33545; 58658</t>
+          <t>34369; 59196</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44453; 65860</t>
+          <t>45110; 65368</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35834; 54253</t>
+          <t>35465; 54474</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65828; 96146</t>
+          <t>64849; 97140</t>
         </is>
       </c>
     </row>
@@ -2513,27 +2513,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5401; 14956</t>
+          <t>6136; 15826</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1396; 8268</t>
+          <t>1336; 8478</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2841</t>
+          <t>0; 2818</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6867; 17216</t>
+          <t>7108; 16786</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2295; 9213</t>
+          <t>2285; 9478</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2543,17 +2543,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14314; 28929</t>
+          <t>15331; 28568</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4495; 14520</t>
+          <t>4688; 14391</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3302</t>
+          <t>0; 2727</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9677; 20711</t>
+          <t>9896; 20768</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14719; 25685</t>
+          <t>14223; 26217</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1459; 8106</t>
+          <t>1428; 8148</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7098; 17057</t>
+          <t>7412; 17830</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12151; 24672</t>
+          <t>12144; 24924</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7091; 18658</t>
+          <t>7547; 19227</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19549; 35087</t>
+          <t>18802; 34175</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29883; 46603</t>
+          <t>29841; 46893</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10537; 23771</t>
+          <t>10603; 23792</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21575; 37685</t>
+          <t>21341; 37970</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>29057; 46432</t>
+          <t>29502; 45835</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23311; 40672</t>
+          <t>23197; 39713</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24427; 41306</t>
+          <t>24574; 41862</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30066; 48698</t>
+          <t>30294; 47435</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35937; 60185</t>
+          <t>36510; 61194</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51228; 74588</t>
+          <t>49499; 73412</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>64150; 89282</t>
+          <t>62085; 88270</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62883; 93988</t>
+          <t>64266; 93621</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>65403; 85973</t>
+          <t>65231; 86195</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>48479; 67573</t>
+          <t>48919; 68202</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2236; 9651</t>
+          <t>2572; 10050</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>80994; 102441</t>
+          <t>81504; 102774</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>44837; 64968</t>
+          <t>44767; 64644</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2801; 11186</t>
+          <t>2870; 11303</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>152101; 181882</t>
+          <t>152428; 182314</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>99972; 126924</t>
+          <t>98981; 127233</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6785; 17616</t>
+          <t>6780; 17541</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>181701; 221031</t>
+          <t>179896; 219776</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>202173; 242461</t>
+          <t>203027; 242223</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>87393; 123999</t>
+          <t>89346; 126675</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>217052; 258778</t>
+          <t>217360; 259166</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>190319; 232392</t>
+          <t>193406; 234009</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>134069; 191362</t>
+          <t>134546; 189991</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>407801; 466932</t>
+          <t>409122; 467887</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>409889; 465742</t>
+          <t>405192; 463161</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>234280; 303437</t>
+          <t>232576; 300917</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$individual-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Provincia-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción individual en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31,43%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44,02%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>17,2%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>47,8%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>27,71%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31,43%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,8; 26,75</t>
+          <t>21,89; 40,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,13; 57,1</t>
+          <t>23,43; 42,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,48; 37,09</t>
+          <t>34,91; 54,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,71; 40,6</t>
+          <t>10,14; 25,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,56; 42,57</t>
+          <t>36,94; 58,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,26; 52,19</t>
+          <t>24,42; 43,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,82; 31,4</t>
+          <t>19,0; 32,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,97; 46,92</t>
+          <t>32,82; 47,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,42; 43,58</t>
+          <t>32,78; 46,35</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37,96%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>20,02%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>39,29%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,96%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,27; 26,76</t>
+          <t>17,8; 30,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,42; 47,4</t>
+          <t>30,8; 45,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,41; 3,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,93; 31,59</t>
+          <t>14,16; 26,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,85; 45,97</t>
+          <t>31,5; 47,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,78</t>
+          <t>0,0; 5,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,56; 26,73</t>
+          <t>18,29; 27,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,3; 44,21</t>
+          <t>33,35; 43,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,89</t>
+          <t>0,54; 3,43</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,95%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17,19%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17,18%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>22,31%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>17,9%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20,19%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,95%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,19%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,16; 32,42</t>
+          <t>13,51; 29,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,28; 26,49</t>
+          <t>10,98; 26,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,55; 29,12</t>
+          <t>10,77; 26,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,77; 29,2</t>
+          <t>14,68; 31,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 26,03</t>
+          <t>9,93; 25,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,31; 24,7</t>
+          <t>12,85; 29,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,43; 27,32</t>
+          <t>15,6; 27,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,55; 23,15</t>
+          <t>12,21; 23,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,57; 24,3</t>
+          <t>13,26; 24,5</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35,81%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26,17%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>58,05%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>31,78%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>30,84%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>47,53%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35,81%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>26,17%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,51; 40,81</t>
+          <t>27,25; 45,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,39; 40,14</t>
+          <t>18,37; 34,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,49; 57,5</t>
+          <t>45,72; 76,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,68; 44,65</t>
+          <t>23,58; 41,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,08; 35,24</t>
+          <t>22,6; 40,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,99; 75,76</t>
+          <t>38,41; 59,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,19; 40,86</t>
+          <t>28,15; 41,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,54; 34,63</t>
+          <t>22,74; 35,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44,03; 65,96</t>
+          <t>43,65; 63,41</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>24,3%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,53%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>22,88%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>9,23%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24,3%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,98; 36,05</t>
+          <t>14,79; 35,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 20,75</t>
+          <t>5,0; 21,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,2; 35,9</t>
+          <t>12,99; 34,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 20,45</t>
+          <t>3,35; 19,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,91; 31,51</t>
+          <t>17,13; 31,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 16,5</t>
+          <t>5,44; 15,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19,7%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30,95%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21,3%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>26,63%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>36,74%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19,7%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>30,95%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,9; 37,56</t>
+          <t>12,02; 28,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26,21; 48,31</t>
+          <t>21,62; 42,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 17,65</t>
+          <t>12,55; 33,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,3; 29,6</t>
+          <t>17,31; 37,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,03; 43,17</t>
+          <t>27,07; 49,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,43; 34,22</t>
+          <t>2,99; 16,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,27; 29,58</t>
+          <t>17,41; 30,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,64; 41,86</t>
+          <t>26,53; 41,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,36; 23,25</t>
+          <t>9,92; 22,25</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22,18%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>27,74%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>32,76%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>21,18%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>27,3%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>24,83%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22,18%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,38; 27,37</t>
+          <t>17,05; 28,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,6; 33,55</t>
+          <t>21,5; 34,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,63; 31,9</t>
+          <t>24,83; 41,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,86; 28,72</t>
+          <t>15,54; 27,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,65; 33,9</t>
+          <t>21,73; 34,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,54; 39,46</t>
+          <t>18,9; 32,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,4; 25,81</t>
+          <t>17,68; 25,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,45; 31,92</t>
+          <t>23,36; 32,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,99; 33,49</t>
+          <t>24,04; 35,05</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>53,74%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>31,92%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>45,93%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>35,35%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>53,74%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>31,92%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>39,8; 52,58</t>
+          <t>47,72; 60,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,8; 41,54</t>
+          <t>26,19; 37,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,64</t>
+          <t>1,84; 7,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47,58; 59,99</t>
+          <t>39,6; 52,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,31; 37,99</t>
+          <t>29,83; 41,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,24</t>
+          <t>1,73; 7,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,47; 54,38</t>
+          <t>45,45; 54,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,6; 38,05</t>
+          <t>29,58; 37,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,1</t>
+          <t>2,19; 5,78</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>31,64%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>28,65%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>20,58%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>28,22%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>31,81%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>16,15%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25,4; 31,03</t>
+          <t>29,13; 34,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29,0; 34,59</t>
+          <t>26,08; 31,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13,43; 19,04</t>
+          <t>17,68; 24,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28,9; 34,45</t>
+          <t>25,48; 30,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26,14; 31,62</t>
+          <t>28,96; 34,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,7; 24,99</t>
+          <t>14,76; 19,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,01; 32,04</t>
+          <t>28,0; 32,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28,13; 32,16</t>
+          <t>28,25; 32,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,32; 21,11</t>
+          <t>16,88; 21,28</t>
         </is>
       </c>
     </row>
@@ -1654,20 +1654,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción individual en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20368</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21027</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28237</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>9708</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>27425</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20308</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20368</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21027</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33079</t>
+          <t>18936</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53387</t>
+          <t>47173</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6096; 15104</t>
+          <t>14186; 26428</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20157; 32758</t>
+          <t>15103; 27495</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13543; 27183</t>
+          <t>22396; 35084</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14071; 26312</t>
+          <t>5725; 14656</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15184; 27439</t>
+          <t>21193; 33368</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24813; 41423</t>
+          <t>13791; 24584</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22822; 38072</t>
+          <t>23041; 38958</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40166; 57169</t>
+          <t>39986; 57932</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43379; 66529</t>
+          <t>39546; 55906</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>41866</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>20837</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>40841</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1662</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26370</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>41866</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3153</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14853; 27850</t>
+          <t>19556; 34002</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32662; 49270</t>
+          <t>33969; 50600</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5422</t>
+          <t>481; 3491</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19706; 34709</t>
+          <t>14740; 27626</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34024; 50695</t>
+          <t>32741; 48982</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>645; 4824</t>
+          <t>0; 5348</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37562; 57195</t>
+          <t>39141; 57966</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71333; 94705</t>
+          <t>71452; 93504</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1405; 7368</t>
+          <t>1172; 7454</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14217</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12016</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>15209</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>11965</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11763</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14217</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12016</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11280</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22960</t>
+          <t>21483</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10334; 22103</t>
+          <t>9624; 20874</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6867; 17702</t>
+          <t>7678; 18333</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7893; 16965</t>
+          <t>6395; 15634</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9096; 20807</t>
+          <t>10011; 21628</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7154; 18197</t>
+          <t>6640; 17114</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6927; 16587</t>
+          <t>7267; 16755</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21515; 38087</t>
+          <t>21757; 37832</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17157; 31657</t>
+          <t>16694; 32145</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17019; 30483</t>
+          <t>15377; 28399</t>
         </is>
       </c>
     </row>
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29447</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21243</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>41890</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>24716</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>23476</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>32867</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29447</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21243</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45654</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>78521</t>
+          <t>76209</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18279; 31736</t>
+          <t>22411; 37542</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17048; 30560</t>
+          <t>14915; 28243</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25925; 39756</t>
+          <t>32994; 55090</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21941; 36714</t>
+          <t>18338; 31899</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15487; 28608</t>
+          <t>17207; 30731</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34369; 59196</t>
+          <t>26797; 41767</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45110; 65368</t>
+          <t>45034; 65670</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35465; 54474</t>
+          <t>35767; 55267</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64849; 97140</t>
+          <t>61947; 89998</t>
         </is>
       </c>
     </row>
@@ -2407,32 +2407,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11363</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4880</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>10044</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>3773</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>553</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>11363</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4880</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>552</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>552</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6136; 15826</t>
+          <t>6914; 16778</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1336; 8478</t>
+          <t>2316; 9980</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2818</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7108; 16786</t>
+          <t>5705; 15208</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2285; 9478</t>
+          <t>1367; 8096</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2779</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15331; 28568</t>
+          <t>15531; 28471</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4688; 14391</t>
+          <t>4748; 13733</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2727</t>
+          <t>0; 3035</t>
         </is>
       </c>
     </row>
@@ -2570,32 +2570,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>11866</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>17869</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10425</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>14726</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>19941</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4056</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>11866</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>17869</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>14463</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9896; 20768</t>
+          <t>7240; 17428</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14223; 26217</t>
+          <t>12483; 24616</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1428; 8148</t>
+          <t>6142; 16565</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7412; 17830</t>
+          <t>9573; 20635</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12144; 24924</t>
+          <t>14689; 26755</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7547; 19227</t>
+          <t>1369; 7679</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18802; 34175</t>
+          <t>20114; 35334</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29841; 46893</t>
+          <t>29715; 46078</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10603; 23792</t>
+          <t>9391; 21069</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>32329</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>38812</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>45992</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>29385</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>37288</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>30919</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>32329</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>38812</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46376</t>
+          <t>30770</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>77295</t>
+          <t>76762</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21341; 37970</t>
+          <t>24852; 42067</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>29502; 45835</t>
+          <t>30077; 48281</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23197; 39713</t>
+          <t>34859; 57735</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24574; 41862</t>
+          <t>21555; 37581</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30294; 47435</t>
+          <t>29684; 46814</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36510; 61194</t>
+          <t>23164; 40240</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49499; 73412</t>
+          <t>50299; 73032</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>62085; 88270</t>
+          <t>64601; 88680</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>64266; 93621</t>
+          <t>63208; 92150</t>
         </is>
       </c>
     </row>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>91</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>92061</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>54326</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>5765</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>75284</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>58037</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>5303</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>92061</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>54326</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>10982</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>65231; 86195</t>
+          <t>81757; 103507</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>48919; 68202</t>
+          <t>44577; 64227</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2572; 10050</t>
+          <t>2925; 11243</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>81504; 102774</t>
+          <t>64910; 85955</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>44767; 64644</t>
+          <t>48981; 68459</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2870; 11303</t>
+          <t>2428; 10298</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>152428; 182314</t>
+          <t>152367; 181431</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>98981; 127233</t>
+          <t>98916; 125677</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6780; 17541</t>
+          <t>6557; 17311</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>342</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>154</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>238021</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>212039</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>143920</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>199908</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>222745</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>107431</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>238021</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>212039</t>
-        </is>
-      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>156315</t>
+          <t>106858</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>263747</t>
+          <t>250778</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>179896; 219776</t>
+          <t>219149; 259581</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>203027; 242223</t>
+          <t>193026; 230708</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>89346; 126675</t>
+          <t>123615; 172157</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>217360; 259166</t>
+          <t>180444; 219171</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>193406; 234009</t>
+          <t>202777; 242038</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>134546; 189991</t>
+          <t>92798; 123777</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>409122; 467887</t>
+          <t>409018; 467293</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>405192; 463161</t>
+          <t>406858; 464447</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>232576; 300917</t>
+          <t>224131; 282524</t>
         </is>
       </c>
     </row>
